--- a/docker_tests/fixtures/testB.xlsx
+++ b/docker_tests/fixtures/testB.xlsx
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:L65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -491,6 +491,9 @@
       <c r="K1" t="str">
         <v>constraint_message</v>
       </c>
+      <c r="L1" t="str">
+        <v>calculation</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -848,16 +851,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>begin_group</v>
+        <v>calculate</v>
       </c>
       <c r="B12" t="str">
-        <v>group_lt58n55</v>
+        <v>NO_TC_project-alpha</v>
       </c>
       <c r="C12" t="str">
-        <v>Deine Fähigkeiten und Erfahrungen</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>Your skills and experiences</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -866,7 +869,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>false</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -879,20 +882,23 @@
       </c>
       <c r="K12" t="str">
         <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>if(selected(${project_id}, 'project-alpha') and not(selected(${project_role_project-alpha}, 'team_coordinator')), 'Alpha: Not TC', '')</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>begin_group</v>
+        <v>calculate</v>
       </c>
       <c r="B13" t="str">
-        <v>rating_technologies_tools</v>
+        <v>TT_project-alpha</v>
       </c>
       <c r="C13" t="str">
-        <v>Tools</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>Tools</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +907,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>false</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -914,32 +920,35 @@
       </c>
       <c r="K13" t="str">
         <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>if(selected(${project_id}, 'project-alpha') and selected(${project_role_project-alpha}, 'team_trainee'), 'Alpha: TT', '')</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>select_one iy6st81</v>
+        <v>calculate</v>
       </c>
       <c r="B14" t="str">
-        <v>rating_technologies_tools_header</v>
+        <v>missing_coord</v>
       </c>
       <c r="C14" t="str">
-        <v>Bitte bewerte Deine Erfahrung mit den folgenden Technologien und Tools:</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>Please rate your experience with the following technologies and tools:</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>false</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>label</v>
+        <v/>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -949,20 +958,23 @@
       </c>
       <c r="K14" t="str">
         <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>normalize-space(concat(${NO_TC_project-alpha}, if(${NO_TC_project-alpha} != '' and ${TT_project-alpha} != '', ', ', ''), ${TT_project-alpha}))</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>select_one iy6st81</v>
+        <v>begin_group</v>
       </c>
       <c r="B15" t="str">
-        <v>sosci_survey</v>
+        <v>group_lt58n55</v>
       </c>
       <c r="C15" t="str">
-        <v>SoSci Survey</v>
+        <v>Deine Fähigkeiten und Erfahrungen</v>
       </c>
       <c r="D15" t="str">
-        <v>SoSci Survey</v>
+        <v>Your skills and experiences</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -971,13 +983,13 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H15" t="str">
-        <v>list-nolabel</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -988,16 +1000,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>select_one iy6st81</v>
+        <v>begin_group</v>
       </c>
       <c r="B16" t="str">
-        <v>python</v>
+        <v>rating_technologies_tools</v>
       </c>
       <c r="C16" t="str">
-        <v>Python</v>
+        <v>Tools</v>
       </c>
       <c r="D16" t="str">
-        <v>Python</v>
+        <v>Tools</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1006,13 +1018,13 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H16" t="str">
-        <v>list-nolabel</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1026,28 +1038,28 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B17" t="str">
-        <v>rstats</v>
+        <v>rating_technologies_tools_header</v>
       </c>
       <c r="C17" t="str">
-        <v>R</v>
+        <v>Bitte bewerte Deine Erfahrung mit den folgenden Technologien und Tools:</v>
       </c>
       <c r="D17" t="str">
-        <v>R</v>
+        <v>Please rate your experience with the following technologies and tools:</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="G17" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H17" t="str">
-        <v>list-nolabel</v>
+        <v>label</v>
       </c>
       <c r="I17" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1061,13 +1073,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B18" t="str">
-        <v>powerbi</v>
+        <v>sosci_survey</v>
       </c>
       <c r="C18" t="str">
-        <v>Power BI</v>
+        <v>SoSci Survey</v>
       </c>
       <c r="D18" t="str">
-        <v>Power BI</v>
+        <v>SoSci Survey</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1082,7 +1094,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I18" t="str">
-        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1096,13 +1108,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B19" t="str">
-        <v>excel</v>
+        <v>python</v>
       </c>
       <c r="C19" t="str">
-        <v>Microsoft Excel</v>
+        <v>Python</v>
       </c>
       <c r="D19" t="str">
-        <v>Microsoft Excel</v>
+        <v>Python</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1117,7 +1129,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I19" t="str">
-        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
+        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1131,13 +1143,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B20" t="str">
-        <v>sql</v>
+        <v>rstats</v>
       </c>
       <c r="C20" t="str">
-        <v>SQL</v>
+        <v>R</v>
       </c>
       <c r="D20" t="str">
-        <v>SQL</v>
+        <v>R</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1152,7 +1164,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I20" t="str">
-        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
+        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1166,13 +1178,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B21" t="str">
-        <v>git</v>
+        <v>powerbi</v>
       </c>
       <c r="C21" t="str">
-        <v>Git</v>
+        <v>Power BI</v>
       </c>
       <c r="D21" t="str">
-        <v>Git</v>
+        <v>Power BI</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1187,7 +1199,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I21" t="str">
-        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
+        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1201,13 +1213,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B22" t="str">
-        <v>jupyter</v>
+        <v>excel</v>
       </c>
       <c r="C22" t="str">
-        <v>Jupyter Notebooks</v>
+        <v>Microsoft Excel</v>
       </c>
       <c r="D22" t="str">
-        <v>Jupyter Notebooks</v>
+        <v>Microsoft Excel</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1222,7 +1234,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I22" t="str">
-        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
+        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1236,13 +1248,13 @@
         <v>select_one iy6st81</v>
       </c>
       <c r="B23" t="str">
-        <v>tensorflow</v>
+        <v>sql</v>
       </c>
       <c r="C23" t="str">
-        <v>TensorFlow / PyTorch</v>
+        <v>SQL</v>
       </c>
       <c r="D23" t="str">
-        <v>TensorFlow / PyTorch</v>
+        <v>SQL</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1257,7 +1269,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I23" t="str">
-        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
+        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1268,31 +1280,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>text</v>
+        <v>select_one iy6st81</v>
       </c>
       <c r="B24" t="str">
-        <v>tools_other</v>
+        <v>git</v>
       </c>
       <c r="C24" t="str">
-        <v>Andere relevante Tools</v>
+        <v>Git</v>
       </c>
       <c r="D24" t="str">
-        <v>Other relevant tools</v>
+        <v>Git</v>
       </c>
       <c r="E24" t="str">
-        <v>Bitte gib hier andere Tools an, die du kennst und die du für relevant erachtest.</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>Please specifiy other tools you know that you consider relevant</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H24" t="str">
-        <v>multiline</v>
+        <v>list-nolabel</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1303,16 +1315,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>end_group</v>
+        <v>select_one iy6st81</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>jupyter</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>Jupyter Notebooks</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>Jupyter Notebooks</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1321,13 +1333,13 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>list-nolabel</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1338,16 +1350,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>begin_group</v>
+        <v>select_one iy6st81</v>
       </c>
       <c r="B26" t="str">
-        <v>rating_techniques</v>
+        <v>tensorflow</v>
       </c>
       <c r="C26" t="str">
-        <v>Techniken</v>
+        <v>TensorFlow / PyTorch</v>
       </c>
       <c r="D26" t="str">
-        <v>Techniques</v>
+        <v>TensorFlow / PyTorch</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1356,13 +1368,13 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H26" t="str">
-        <v>field-list</v>
+        <v>list-nolabel</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1373,28 +1385,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>select_one xe9mo32</v>
+        <v>text</v>
       </c>
       <c r="B27" t="str">
-        <v>rating_techniques_header</v>
+        <v>tools_other</v>
       </c>
       <c r="C27" t="str">
-        <v>Bitte bewerte Deine Erfahrung mit den folgenden Techniken.</v>
+        <v>Andere relevante Tools</v>
       </c>
       <c r="D27" t="str">
-        <v>Please rate your experience with the following techniques:</v>
+        <v>Other relevant tools</v>
       </c>
       <c r="E27" t="str">
-        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v>Bitte gib hier andere Tools an, die du kennst und die du für relevant erachtest.</v>
       </c>
       <c r="F27" t="str">
-        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v>Please specifiy other tools you know that you consider relevant</v>
       </c>
       <c r="G27" t="str">
         <v>false</v>
       </c>
       <c r="H27" t="str">
-        <v>label</v>
+        <v>multiline</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1408,16 +1420,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>select_one xe9mo32</v>
+        <v>end_group</v>
       </c>
       <c r="B28" t="str">
-        <v>survey_design</v>
+        <v/>
       </c>
       <c r="C28" t="str">
-        <v>Entwicklung von Fragebögen</v>
+        <v/>
       </c>
       <c r="D28" t="str">
-        <v>Survey design</v>
+        <v/>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1426,13 +1438,13 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>true</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>list-nolabel</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1443,16 +1455,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>select_one xe9mo32</v>
+        <v>begin_group</v>
       </c>
       <c r="B29" t="str">
-        <v>indicator_development</v>
+        <v>rating_techniques</v>
       </c>
       <c r="C29" t="str">
-        <v>Entwicklung von Indikatoren</v>
+        <v>Techniken</v>
       </c>
       <c r="D29" t="str">
-        <v>Development of indicators</v>
+        <v>Techniques</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1461,13 +1473,13 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H29" t="str">
-        <v>list-nolabel</v>
+        <v>field-list</v>
       </c>
       <c r="I29" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1481,28 +1493,28 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B30" t="str">
-        <v>data_collection</v>
+        <v>rating_techniques_header</v>
       </c>
       <c r="C30" t="str">
-        <v>Datenerhebung</v>
+        <v>Bitte bewerte Deine Erfahrung mit den folgenden Techniken.</v>
       </c>
       <c r="D30" t="str">
-        <v>Data collection</v>
+        <v>Please rate your experience with the following techniques:</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="G30" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H30" t="str">
-        <v>list-nolabel</v>
+        <v>label</v>
       </c>
       <c r="I30" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1516,13 +1528,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B31" t="str">
-        <v>data_cleaning</v>
+        <v>survey_design</v>
       </c>
       <c r="C31" t="str">
-        <v>Datenbereinigung</v>
+        <v>Entwicklung von Fragebögen</v>
       </c>
       <c r="D31" t="str">
-        <v>Data cleaning</v>
+        <v>Survey design</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1537,7 +1549,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I31" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1551,13 +1563,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B32" t="str">
-        <v>descriptive_statistics</v>
+        <v>indicator_development</v>
       </c>
       <c r="C32" t="str">
-        <v>Deskriptive Statistik</v>
+        <v>Entwicklung von Indikatoren</v>
       </c>
       <c r="D32" t="str">
-        <v>Descriptive statistics</v>
+        <v>Development of indicators</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1572,7 +1584,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I32" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1586,13 +1598,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B33" t="str">
-        <v>data_visualization</v>
+        <v>data_collection</v>
       </c>
       <c r="C33" t="str">
-        <v>Datenvisualisierung</v>
+        <v>Datenerhebung</v>
       </c>
       <c r="D33" t="str">
-        <v>Data visualization</v>
+        <v>Data collection</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1607,7 +1619,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I33" t="str">
-        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1621,13 +1633,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B34" t="str">
-        <v>data_engineering</v>
+        <v>data_cleaning</v>
       </c>
       <c r="C34" t="str">
-        <v>Data Engineering</v>
+        <v>Datenbereinigung</v>
       </c>
       <c r="D34" t="str">
-        <v>Data engineering</v>
+        <v>Data cleaning</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1642,7 +1654,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I34" t="str">
-        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
+        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1656,13 +1668,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B35" t="str">
-        <v>automation</v>
+        <v>descriptive_statistics</v>
       </c>
       <c r="C35" t="str">
-        <v>Automatisierung</v>
+        <v>Deskriptive Statistik</v>
       </c>
       <c r="D35" t="str">
-        <v>Automation</v>
+        <v>Descriptive statistics</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1677,7 +1689,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I35" t="str">
-        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
+        <v>selected(${project_role_project-alpha}, 'role-data-analysis')</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1691,13 +1703,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B36" t="str">
-        <v>projectplanning</v>
+        <v>data_visualization</v>
       </c>
       <c r="C36" t="str">
-        <v>Projektplanung</v>
+        <v>Datenvisualisierung</v>
       </c>
       <c r="D36" t="str">
-        <v>Project planning</v>
+        <v>Data visualization</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1712,7 +1724,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I36" t="str">
-        <v>selected(${project_role_project-gamma}, 'role-project-management')</v>
+        <v>selected(${project_role_project-beta}, 'role-visualization')</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1726,13 +1738,13 @@
         <v>select_one xe9mo32</v>
       </c>
       <c r="B37" t="str">
-        <v>mlmodeling</v>
+        <v>data_engineering</v>
       </c>
       <c r="C37" t="str">
-        <v>ML-Modellierung</v>
+        <v>Data Engineering</v>
       </c>
       <c r="D37" t="str">
-        <v>ML modeling</v>
+        <v>Data engineering</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1747,7 +1759,7 @@
         <v>list-nolabel</v>
       </c>
       <c r="I37" t="str">
-        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
+        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1758,16 +1770,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>end_group</v>
+        <v>select_one xe9mo32</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>automation</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>Automatisierung</v>
       </c>
       <c r="D38" t="str">
-        <v/>
+        <v>Automation</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1776,13 +1788,13 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>list-nolabel</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>selected(${project_role_project-beta}, 'role-data-engineering')</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1793,16 +1805,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>begin_group</v>
+        <v>select_one xe9mo32</v>
       </c>
       <c r="B39" t="str">
-        <v>rating_topics</v>
+        <v>projectplanning</v>
       </c>
       <c r="C39" t="str">
-        <v>Themen</v>
+        <v>Projektplanung</v>
       </c>
       <c r="D39" t="str">
-        <v>Topics</v>
+        <v>Project planning</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1811,13 +1823,13 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H39" t="str">
-        <v>field-list</v>
+        <v>list-nolabel</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>selected(${project_role_project-gamma}, 'role-project-management')</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -1828,31 +1840,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>select_one dm1uu76</v>
+        <v>select_one xe9mo32</v>
       </c>
       <c r="B40" t="str">
-        <v>rating_topics_header</v>
+        <v>mlmodeling</v>
       </c>
       <c r="C40" t="str">
-        <v>Bitte bewerte Deine Erfahrung mit den folgenden Themen:</v>
+        <v>ML-Modellierung</v>
       </c>
       <c r="D40" t="str">
-        <v>Please rate your experience with the following topics:</v>
+        <v>ML modeling</v>
       </c>
       <c r="E40" t="str">
-        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H40" t="str">
-        <v>label</v>
+        <v>list-nolabel</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>selected(${project_role_project-gamma}, 'role-machine-learning')</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -1863,16 +1875,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>select_one dm1uu76</v>
+        <v>end_group</v>
       </c>
       <c r="B41" t="str">
-        <v>wirkungsmessung</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>Wirkungsmessung</v>
+        <v/>
       </c>
       <c r="D41" t="str">
-        <v>Impact Measurement</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1881,13 +1893,13 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>true</v>
+        <v/>
       </c>
       <c r="H41" t="str">
-        <v>list-nolabel</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -1898,16 +1910,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>select_one dm1uu76</v>
+        <v>begin_group</v>
       </c>
       <c r="B42" t="str">
-        <v>research_design</v>
+        <v>rating_topics</v>
       </c>
       <c r="C42" t="str">
-        <v>Research Design</v>
+        <v>Themen</v>
       </c>
       <c r="D42" t="str">
-        <v>Research Design</v>
+        <v>Topics</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1916,13 +1928,13 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H42" t="str">
-        <v>list-nolabel</v>
+        <v>field-list</v>
       </c>
       <c r="I42" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -1936,28 +1948,28 @@
         <v>select_one dm1uu76</v>
       </c>
       <c r="B43" t="str">
-        <v>survey_research</v>
+        <v>rating_topics_header</v>
       </c>
       <c r="C43" t="str">
-        <v>Umfrageforschung</v>
+        <v>Bitte bewerte Deine Erfahrung mit den folgenden Themen:</v>
       </c>
       <c r="D43" t="str">
-        <v>Survey Research</v>
+        <v>Please rate your experience with the following topics:</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Hier kannst du  mehr darüber lesen, wie wir die verschiedenen Erfahrungsstufen definieren: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>Read more about what the different experience labels mean for us: https://docs.correlaid.org/project-manual/data4good-projects#experience-scale</v>
       </c>
       <c r="G43" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H43" t="str">
-        <v>list-nolabel</v>
+        <v>label</v>
       </c>
       <c r="I43" t="str">
-        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
+        <v/>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -1971,13 +1983,13 @@
         <v>select_one dm1uu76</v>
       </c>
       <c r="B44" t="str">
-        <v>data_protection</v>
+        <v>wirkungsmessung</v>
       </c>
       <c r="C44" t="str">
-        <v>Datenschutz</v>
+        <v>Wirkungsmessung</v>
       </c>
       <c r="D44" t="str">
-        <v>Data protection</v>
+        <v>Impact Measurement</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2006,13 +2018,13 @@
         <v>select_one dm1uu76</v>
       </c>
       <c r="B45" t="str">
-        <v>resilience_mental_health</v>
+        <v>research_design</v>
       </c>
       <c r="C45" t="str">
-        <v>Resilienz und Mentale Gesundheit</v>
+        <v>Research Design</v>
       </c>
       <c r="D45" t="str">
-        <v>Resilience and mental health</v>
+        <v>Research Design</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2041,13 +2053,13 @@
         <v>select_one dm1uu76</v>
       </c>
       <c r="B46" t="str">
-        <v>education_research</v>
+        <v>survey_research</v>
       </c>
       <c r="C46" t="str">
-        <v>Bildungsforschung o.ä.</v>
+        <v>Umfrageforschung</v>
       </c>
       <c r="D46" t="str">
-        <v>Education research (or similar)</v>
+        <v>Survey Research</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2073,16 +2085,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>end_group</v>
+        <v>select_one dm1uu76</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>data_protection</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>Datenschutz</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>Data protection</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2091,13 +2103,13 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>list-nolabel</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2108,16 +2120,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>begin_group</v>
+        <v>select_one dm1uu76</v>
       </c>
       <c r="B48" t="str">
-        <v>group_pr7pr34</v>
+        <v>resilience_mental_health</v>
       </c>
       <c r="C48" t="str">
-        <v>Du und das Projekt</v>
+        <v>Resilienz und Mentale Gesundheit</v>
       </c>
       <c r="D48" t="str">
-        <v>You and the project</v>
+        <v>Resilience and mental health</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2126,13 +2138,13 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>list-nolabel</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2143,31 +2155,31 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>text</v>
+        <v>select_one dm1uu76</v>
       </c>
       <c r="B49" t="str">
-        <v>motivation_skills</v>
+        <v>education_research</v>
       </c>
       <c r="C49" t="str">
-        <v>Bitte beschreibe hier, welche Deiner Fähigkeiten und Erfahrungen Dich besonders für die Teilnahme an diesem Projekt qualifizieren.</v>
+        <v>Bildungsforschung o.ä.</v>
       </c>
       <c r="D49" t="str">
-        <v>Please describe here what skills and experiences you would bring to the project.</v>
+        <v>Education research (or similar)</v>
       </c>
       <c r="E49" t="str">
-        <v>Bitte schreibe maximal 5 Sätze pro Projekt, auf das du dich bewerben möchtest.</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>Please write maximum 5 sentences per project that you are applying to.</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v>true</v>
       </c>
       <c r="H49" t="str">
-        <v>multiline</v>
+        <v>list-nolabel</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>selected(${project_role_project-alpha}, 'role-survey-design')</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2178,28 +2190,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B50" t="str">
-        <v>motivation_why</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>Bitte beschreibe hier, warum Du Dich für dieses Projekt engagieren möchtest.</v>
+        <v/>
       </c>
       <c r="D50" t="str">
-        <v>Please describe here why you want to get involved in this project.</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>Bitte schreibe maximal 5 Sätze pro Projekt, auf das du dich bewerben möchtest.</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>Please write maximum 5 sentences per project that you are applying to.</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>true</v>
+        <v/>
       </c>
       <c r="H50" t="str">
-        <v>multiline</v>
+        <v/>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2213,25 +2225,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>select_one il2wc73</v>
+        <v>begin_group</v>
       </c>
       <c r="B51" t="str">
-        <v>past_applications</v>
+        <v>group_pr7pr34</v>
       </c>
       <c r="C51" t="str">
-        <v>Hast du dich in der Vergangenheit bereits auf CorrelAid-Projekte beworben?</v>
+        <v>Du und das Projekt</v>
       </c>
       <c r="D51" t="str">
-        <v>Have you applied to a CorrelAid project in the past?</v>
+        <v>You and the project</v>
       </c>
       <c r="E51" t="str">
-        <v>Um möglichst vielen Personen die Gelegenheit zu geben, an unseren Projekten teilzunehmen, werden Bewerbungen von bisher unerfolgreichen Personen bei gleicher Eignung bevorzugt behandelt.</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v>In order to give as many people as possible the opportunity to participate in one of our projects, applications of individuals who have unsuccessfully applied in the past are preferred given equal suitability for the project.</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -2251,28 +2263,28 @@
         <v>text</v>
       </c>
       <c r="B52" t="str">
-        <v>past_applications_details</v>
+        <v>motivation_skills</v>
       </c>
       <c r="C52" t="str">
-        <v>Bitte gib hier an, für welche Projekte du dich beworben hast, falls du dich noch erinnern kannst.</v>
+        <v>Bitte beschreibe hier, welche Deiner Fähigkeiten und Erfahrungen Dich besonders für die Teilnahme an diesem Projekt qualifizieren.</v>
       </c>
       <c r="D52" t="str">
-        <v>If you can remember, please specify which project(s) you have applied for.</v>
+        <v>Please describe here what skills and experiences you would bring to the project.</v>
       </c>
       <c r="E52" t="str">
-        <v>Grobe Angaben helfen uns auch schon weiter.</v>
+        <v>Bitte schreibe maximal 5 Sätze pro Projekt, auf das du dich bewerben möchtest.</v>
       </c>
       <c r="F52" t="str">
-        <v>Any information is helpful to us.</v>
+        <v>Please write maximum 5 sentences per project that you are applying to.</v>
       </c>
       <c r="G52" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>multiline</v>
       </c>
       <c r="I52" t="str">
-        <v>${past_applications} = 'not_successful'</v>
+        <v/>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2283,28 +2295,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>end_group</v>
+        <v>text</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>motivation_why</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>Bitte beschreibe hier, warum Du Dich für dieses Projekt engagieren möchtest.</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>Please describe here why you want to get involved in this project.</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>Bitte schreibe maximal 5 Sätze pro Projekt, auf das du dich bewerben möchtest.</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>Please write maximum 5 sentences per project that you are applying to.</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>multiline</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2318,25 +2330,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>end_group</v>
+        <v>select_one il2wc73</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>past_applications</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>Hast du dich in der Vergangenheit bereits auf CorrelAid-Projekte beworben?</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>Have you applied to a CorrelAid project in the past?</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>Um möglichst vielen Personen die Gelegenheit zu geben, an unseren Projekten teilzunehmen, werden Bewerbungen von bisher unerfolgreichen Personen bei gleicher Eignung bevorzugt behandelt.</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>In order to give as many people as possible the opportunity to participate in one of our projects, applications of individuals who have unsuccessfully applied in the past are preferred given equal suitability for the project.</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2353,22 +2365,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B55" t="str">
-        <v>demographics</v>
+        <v>past_applications_details</v>
       </c>
       <c r="C55" t="str">
-        <v>Über dich</v>
+        <v>Bitte gib hier an, für welche Projekte du dich beworben hast, falls du dich noch erinnern kannst.</v>
       </c>
       <c r="D55" t="str">
-        <v>About you</v>
+        <v>If you can remember, please specify which project(s) you have applied for.</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>Grobe Angaben helfen uns auch schon weiter.</v>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>Any information is helpful to us.</v>
       </c>
       <c r="G55" t="str">
         <v>false</v>
@@ -2377,7 +2389,7 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>${past_applications} = 'not_successful'</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2388,16 +2400,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B56" t="str">
-        <v>first_name</v>
+        <v/>
       </c>
       <c r="C56" t="str">
-        <v>Wie lautet dein Vorname?</v>
+        <v/>
       </c>
       <c r="D56" t="str">
-        <v>What is your first name?</v>
+        <v/>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2406,7 +2418,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>true</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2423,16 +2435,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B57" t="str">
-        <v>last_name</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>Wie lautet dein Nachname?</v>
+        <v/>
       </c>
       <c r="D57" t="str">
-        <v>What is your last name?</v>
+        <v/>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2441,7 +2453,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>true</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2458,16 +2470,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>text</v>
+        <v>begin_group</v>
       </c>
       <c r="B58" t="str">
-        <v>email_address</v>
+        <v>demographics</v>
       </c>
       <c r="C58" t="str">
-        <v>Unter welcher E-Mail Adresse können wir dich erreichen?</v>
+        <v>Über dich</v>
       </c>
       <c r="D58" t="str">
-        <v>Which email address can we use to contact you?</v>
+        <v>About you</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2476,7 +2488,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -2485,30 +2497,30 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>regex(., '^[\w-\.]+@([\w-]+\.)+[\w-]{2,}$')</v>
+        <v/>
       </c>
       <c r="K58" t="str">
-        <v>Please specify a valid email address.</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>select_one iy7os66</v>
+        <v>text</v>
       </c>
       <c r="B59" t="str">
-        <v>gender</v>
+        <v>first_name</v>
       </c>
       <c r="C59" t="str">
-        <v>Was ist dein Geschlecht?</v>
+        <v>Wie lautet dein Vorname?</v>
       </c>
       <c r="D59" t="str">
-        <v>What is your gender?</v>
+        <v>What is your first name?</v>
       </c>
       <c r="E59" t="str">
-        <v>Hinweis: Da wir bei CorrelAid nach dem Grundprinzip von Geschlechtergleichberechtigung arbeiten, ist diese Frage für uns besonders wichtig.</v>
+        <v/>
       </c>
       <c r="F59" t="str">
-        <v>Note: We ask this question because we want to foster gender diversity within CorrelAid.</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <v>true</v>
@@ -2531,19 +2543,19 @@
         <v>text</v>
       </c>
       <c r="B60" t="str">
-        <v>gender_self_identification</v>
+        <v>last_name</v>
       </c>
       <c r="C60" t="str">
-        <v>Mein Geschlecht ist:</v>
+        <v>Wie lautet dein Nachname?</v>
       </c>
       <c r="D60" t="str">
-        <v>My gender is:</v>
+        <v>What is your last name?</v>
       </c>
       <c r="E60" t="str">
-        <v>Bitte gebe hier dein Geschlecht an.</v>
+        <v/>
       </c>
       <c r="F60" t="str">
-        <v>Please specify your gender here.</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v>true</v>
@@ -2552,7 +2564,7 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>${gender} = 'self_identification'</v>
+        <v/>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2563,16 +2575,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>end_group</v>
+        <v>text</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>email_address</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Unter welcher E-Mail Adresse können wir dich erreichen?</v>
       </c>
       <c r="D61" t="str">
-        <v/>
+        <v>Which email address can we use to contact you?</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2581,7 +2593,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>true</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -2590,30 +2602,30 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>regex(., '^[\w-\.]+@([\w-]+\.)+[\w-]{2,}$')</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>Please specify a valid email address.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>select_one mj8ty33</v>
+        <v>select_one iy7os66</v>
       </c>
       <c r="B62" t="str">
-        <v>consent_privacy_policy</v>
+        <v>gender</v>
       </c>
       <c r="C62" t="str">
-        <v>Einwilligung in die Datenschutzerklärung</v>
+        <v>Was ist dein Geschlecht?</v>
       </c>
       <c r="D62" t="str">
-        <v>Consent to privacy policy</v>
+        <v>What is your gender?</v>
       </c>
       <c r="E62" t="str">
-        <v>Ich habe den Disclaimer gelesen und erteile hiermit meine Zustimmung zur Erhebung, Verarbeitung und Nutzung meiner personenbezogener Daten (Geschlecht und persönliche Fähigkeiten) zu internen und externen Reporting- und Präsentationszwecken. Daneben erteile ich ausdrücklich die Erlaubnis meine Kontaktdaten (Name und E-Mail) zur Kontaktaufnahme zu nutzen und diese bei erfolgreicher Bewerbung mit dem Projektteam zu teilen.</v>
+        <v>Hinweis: Da wir bei CorrelAid nach dem Grundprinzip von Geschlechtergleichberechtigung arbeiten, ist diese Frage für uns besonders wichtig.</v>
       </c>
       <c r="F62" t="str">
-        <v>I have read the disclaimer and hereby give my consent to the collection, processing and use of my personal data (gender and personal skills) for the team selection process and for internal and external reporting as well as presentation purposes. In addition, I expressly grant permission to use my contact details (name and e-mail) to contact me and to share them with the project team if the application is successful.</v>
+        <v>Note: We ask this question because we want to foster gender diversity within CorrelAid.</v>
       </c>
       <c r="G62" t="str">
         <v>true</v>
@@ -2631,9 +2643,114 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>text</v>
+      </c>
+      <c r="B63" t="str">
+        <v>gender_self_identification</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Mein Geschlecht ist:</v>
+      </c>
+      <c r="D63" t="str">
+        <v>My gender is:</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Bitte gebe hier dein Geschlecht an.</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Please specify your gender here.</v>
+      </c>
+      <c r="G63" t="str">
+        <v>true</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v>${gender} = 'self_identification'</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>end_group</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>select_one mj8ty33</v>
+      </c>
+      <c r="B65" t="str">
+        <v>consent_privacy_policy</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Einwilligung in die Datenschutzerklärung</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Consent to privacy policy</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Ich habe den Disclaimer gelesen und erteile hiermit meine Zustimmung zur Erhebung, Verarbeitung und Nutzung meiner personenbezogener Daten (Geschlecht und persönliche Fähigkeiten) zu internen und externen Reporting- und Präsentationszwecken. Daneben erteile ich ausdrücklich die Erlaubnis meine Kontaktdaten (Name und E-Mail) zur Kontaktaufnahme zu nutzen und diese bei erfolgreicher Bewerbung mit dem Projektteam zu teilen.</v>
+      </c>
+      <c r="F65" t="str">
+        <v>I have read the disclaimer and hereby give my consent to the collection, processing and use of my personal data (gender and personal skills) for the team selection process and for internal and external reporting as well as presentation purposes. In addition, I expressly grant permission to use my contact details (name and e-mail) to contact me and to share them with the project team if the application is successful.</v>
+      </c>
+      <c r="G65" t="str">
+        <v>true</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L65"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9411,7 +9528,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9847,9 +9964,93 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>cl-role-project-alpha</v>
+      </c>
+      <c r="B32" t="str">
+        <v>team_coordinator</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Teamkoordinator:in</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Team Coordinator</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>cl-role-project-alpha</v>
+      </c>
+      <c r="B33" t="str">
+        <v>team_trainee</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Team Trainee</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Team Trainee</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>cl-role-project-beta</v>
+      </c>
+      <c r="B34" t="str">
+        <v>team_coordinator</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Teamkoordinator:in</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Team Coordinator</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>cl-role-project-beta</v>
+      </c>
+      <c r="B35" t="str">
+        <v>team_trainee</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Team Trainee</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Team Trainee</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>cl-role-project-gamma</v>
+      </c>
+      <c r="B36" t="str">
+        <v>team_coordinator</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Teamkoordinator:in</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Team Coordinator</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>cl-role-project-gamma</v>
+      </c>
+      <c r="B37" t="str">
+        <v>team_trainee</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Team Trainee</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Team Trainee</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>
